--- a/etf_holdings/2026-09-03_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:16</t>
+          <t>2026-09-03 00:54:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:18</t>
+          <t>2026-09-03 00:54:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:19</t>
+          <t>2026-09-03 00:54:32</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:20</t>
+          <t>2026-09-03 00:54:33</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:20</t>
+          <t>2026-09-03 00:54:33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:20</t>
+          <t>2026-09-03 00:54:33</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:20</t>
+          <t>2026-09-03 00:54:33</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:20</t>
+          <t>2026-09-03 00:54:33</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:29</t>
+          <t>2026-09-03 01:14:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:29</t>
+          <t>2026-09-03 01:14:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:29</t>
+          <t>2026-09-03 01:14:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:29</t>
+          <t>2026-09-03 01:14:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:29</t>
+          <t>2026-09-03 01:14:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:29</t>
+          <t>2026-09-03 01:14:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:29</t>
+          <t>2026-09-03 01:14:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:29</t>
+          <t>2026-09-03 01:14:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:29</t>
+          <t>2026-09-03 01:14:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:29</t>
+          <t>2026-09-03 01:14:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:29</t>
+          <t>2026-09-03 01:14:06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:29</t>
+          <t>2026-09-03 01:14:06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:29</t>
+          <t>2026-09-03 01:14:06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:29</t>
+          <t>2026-09-03 01:14:06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:29</t>
+          <t>2026-09-03 01:14:06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:30</t>
+          <t>2026-09-03 01:14:07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:30</t>
+          <t>2026-09-03 01:14:07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:30</t>
+          <t>2026-09-03 01:14:07</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:30</t>
+          <t>2026-09-03 01:14:07</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:30</t>
+          <t>2026-09-03 01:14:07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:30</t>
+          <t>2026-09-03 01:14:07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:30</t>
+          <t>2026-09-03 01:14:07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:30</t>
+          <t>2026-09-03 01:14:07</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:30</t>
+          <t>2026-09-03 01:14:07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:30</t>
+          <t>2026-09-03 01:14:07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:30</t>
+          <t>2026-09-03 01:14:07</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:30</t>
+          <t>2026-09-03 01:14:07</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:30</t>
+          <t>2026-09-03 01:14:07</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:30</t>
+          <t>2026-09-03 01:14:07</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:30</t>
+          <t>2026-09-03 01:14:07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:32</t>
+          <t>2026-09-03 01:14:08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:32</t>
+          <t>2026-09-03 01:14:08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:32</t>
+          <t>2026-09-03 01:14:08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:32</t>
+          <t>2026-09-03 01:14:08</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:32</t>
+          <t>2026-09-03 01:14:08</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:32</t>
+          <t>2026-09-03 01:14:08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:32</t>
+          <t>2026-09-03 01:14:08</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:32</t>
+          <t>2026-09-03 01:14:08</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:32</t>
+          <t>2026-09-03 01:14:08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:32</t>
+          <t>2026-09-03 01:14:08</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:32</t>
+          <t>2026-09-03 01:14:08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:32</t>
+          <t>2026-09-03 01:14:08</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:32</t>
+          <t>2026-09-03 01:14:08</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:32</t>
+          <t>2026-09-03 01:14:08</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:32</t>
+          <t>2026-09-03 01:14:08</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:33</t>
+          <t>2026-09-03 01:14:09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:33</t>
+          <t>2026-09-03 01:14:09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:33</t>
+          <t>2026-09-03 01:14:09</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:33</t>
+          <t>2026-09-03 01:14:09</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:33</t>
+          <t>2026-09-03 01:14:09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:06</t>
+          <t>2026-09-03 21:41:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-2.25%2385</t>
+          <t>+0.21%2390</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2385</v>
+        <v>2390</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:06</t>
+          <t>2026-09-03 21:41:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0%2610</t>
+          <t>-5.17%2475</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-5.17%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2610</v>
+        <v>2475</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:06</t>
+          <t>2026-09-03 21:41:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.93%3310</t>
+          <t>-0.3%3300</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3310</v>
+        <v>3300</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:06</t>
+          <t>2026-09-03 21:41:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.46%5445</t>
+          <t>-2.85%5290</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5445</v>
+        <v>5290</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:06</t>
+          <t>2026-09-03 21:41:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.93%4275</t>
+          <t>+1.52%4340</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4275</v>
+        <v>4340</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:06</t>
+          <t>2026-09-03 21:41:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.21%973</t>
+          <t>-5.14%923</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-5.14%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>973</v>
+        <v>923</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:06</t>
+          <t>2026-09-03 21:41:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-7.24%1730</t>
+          <t>+1.73%1760</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-7.24%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1730</v>
+        <v>1760</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:06</t>
+          <t>2026-09-03 21:41:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.01%13865</t>
+          <t>-2.99%13450</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>13865</v>
+        <v>13450</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:06</t>
+          <t>2026-09-03 21:41:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.67%5895</t>
+          <t>-1.61%5800</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5895</v>
+        <v>5800</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:06</t>
+          <t>2026-09-03 21:41:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.76%1410</t>
+          <t>-4.61%1345</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.76%</t>
+          <t>-4.61%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1410</v>
+        <v>1345</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:06</t>
+          <t>2026-09-03 21:41:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-2.95%2140</t>
+          <t>-2.34%2090</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2140</v>
+        <v>2090</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:06</t>
+          <t>2026-09-03 21:41:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.04%1200</t>
+          <t>-10%1080</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1200</v>
+        <v>1080</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:06</t>
+          <t>2026-09-03 21:41:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.22%5290</t>
+          <t>-4.63%5045</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-4.63%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5290</v>
+        <v>5045</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:06</t>
+          <t>2026-09-03 21:41:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-7.66%2110</t>
+          <t>-0.71%2095</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-7.66%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2110</v>
+        <v>2095</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:06</t>
+          <t>2026-09-03 21:41:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-3.44%589</t>
+          <t>0%589</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:07</t>
+          <t>2026-09-03 21:41:51</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+3.03%7810</t>
+          <t>-8.45%7150</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>-8.45%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>7810</v>
+        <v>7150</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:07</t>
+          <t>2026-09-03 21:41:51</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-4.08%1175</t>
+          <t>-6.38%1100</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-4.08%</t>
+          <t>-6.38%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1175</v>
+        <v>1100</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:07</t>
+          <t>2026-09-03 21:41:51</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+3.53%17725</t>
+          <t>+0.71%17850</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>17725</v>
+        <v>17850</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:07</t>
+          <t>2026-09-03 21:41:51</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-4.93%540</t>
+          <t>-5.37%511</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-4.93%</t>
+          <t>-5.37%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>540</v>
+        <v>511</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:07</t>
+          <t>2026-09-03 21:41:51</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-1.95%5770</t>
+          <t>-2.69%5615</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-2.69%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5770</v>
+        <v>5615</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:07</t>
+          <t>2026-09-03 21:41:51</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.67%692</t>
+          <t>-2.6%674</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.67%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:07</t>
+          <t>2026-09-03 21:41:51</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-6.26%2170</t>
+          <t>-3.23%2100</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-6.26%</t>
+          <t>-3.23%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2170</v>
+        <v>2100</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:07</t>
+          <t>2026-09-03 21:41:51</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-2.71%1975</t>
+          <t>+2.03%2015</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1975</v>
+        <v>2015</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:07</t>
+          <t>2026-09-03 21:41:51</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-5.23%507</t>
+          <t>-8.48%464</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.23%</t>
+          <t>-8.48%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>507</v>
+        <v>464</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:07</t>
+          <t>2026-09-03 21:41:51</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+7.66%1265</t>
+          <t>-6.32%1185</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+7.66%</t>
+          <t>-6.32%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1265</v>
+        <v>1185</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:07</t>
+          <t>2026-09-03 21:41:51</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.88%3395</t>
+          <t>-8.1%3120</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3395</v>
+        <v>3120</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:07</t>
+          <t>2026-09-03 21:41:51</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0%518</t>
+          <t>-7.82%477.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-7.82%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>518</v>
+        <v>477.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:07</t>
+          <t>2026-09-03 21:41:51</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+4.83%315</t>
+          <t>-5.08%299</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+4.83%</t>
+          <t>-5.08%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:07</t>
+          <t>2026-09-03 21:41:51</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.55%1340</t>
+          <t>-2.99%1300</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1340</v>
+        <v>1300</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:07</t>
+          <t>2026-09-03 21:41:51</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.22%968</t>
+          <t>-2.07%948</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>968</v>
+        <v>948</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:08</t>
+          <t>2026-09-03 21:41:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.28%237.5</t>
+          <t>-6.95%221</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-6.95%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>237.5</v>
+        <v>221</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:08</t>
+          <t>2026-09-03 21:41:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.63%543</t>
+          <t>-2.95%527</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:08</t>
+          <t>2026-09-03 21:41:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.18%112</t>
+          <t>+3.13%115.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>+3.13%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>112</v>
+        <v>115.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:08</t>
+          <t>2026-09-03 21:41:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.42%708</t>
+          <t>-0.71%703</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:08</t>
+          <t>2026-09-03 21:41:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-9.28%2395</t>
+          <t>-2.71%2330</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-9.28%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2395</v>
+        <v>2330</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:08</t>
+          <t>2026-09-03 21:41:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.36%1445</t>
+          <t>-2.77%1405</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.36%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1445</v>
+        <v>1405</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:08</t>
+          <t>2026-09-03 21:41:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-4.91%126</t>
+          <t>-0.79%125</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:08</t>
+          <t>2026-09-03 21:41:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-5.38%704</t>
+          <t>+0.99%711</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-5.38%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:08</t>
+          <t>2026-09-03 21:41:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-2.07%1420</t>
+          <t>-5.28%1345</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>-5.28%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1420</v>
+        <v>1345</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:08</t>
+          <t>2026-09-03 21:41:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.38%1305</t>
+          <t>+3.45%1350</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>+3.45%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1305</v>
+        <v>1350</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:08</t>
+          <t>2026-09-03 21:41:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.1%957</t>
+          <t>-4.7%912</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>957</v>
+        <v>912</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:08</t>
+          <t>2026-09-03 21:41:52</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.51%296.5</t>
+          <t>-3.54%286</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.54%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>296.5</v>
+        <v>286</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:08</t>
+          <t>2026-09-03 21:41:52</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-2.82%2065</t>
+          <t>-3.15%2000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>-3.15%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2065</v>
+        <v>2000</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:08</t>
+          <t>2026-09-03 21:41:52</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.12%412.5</t>
+          <t>-4.24%395</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-4.24%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>412.5</v>
+        <v>395</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:08</t>
+          <t>2026-09-03 21:41:52</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0%744</t>
+          <t>-4.97%707</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.97%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>744</v>
+        <v>707</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:09</t>
+          <t>2026-09-03 21:41:54</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.93%535</t>
+          <t>-1.5%527</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>527</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:09</t>
+          <t>2026-09-03 21:41:54</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3317,17 +3317,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+9.92%3435</t>
+          <t>-2.47%3350</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+9.92%</t>
+          <t>-2.47%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:09</t>
+          <t>2026-09-03 21:41:54</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3380,17 +3380,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+1.7%179</t>
+          <t>-5.59%169</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>-5.59%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>169</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:09</t>
+          <t>2026-09-03 21:41:54</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3443,17 +3443,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-3.46%1395</t>
+          <t>-1.43%1375</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:09</t>
+          <t>2026-09-03 21:41:54</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3506,17 +3506,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1.1%137.5</t>
+          <t>+0.36%138</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:49</t>
+          <t>2026-09-03 21:59:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:49</t>
+          <t>2026-09-03 21:59:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:49</t>
+          <t>2026-09-03 21:59:04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:49</t>
+          <t>2026-09-03 21:59:04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:49</t>
+          <t>2026-09-03 21:59:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:49</t>
+          <t>2026-09-03 21:59:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:49</t>
+          <t>2026-09-03 21:59:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:49</t>
+          <t>2026-09-03 21:59:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:49</t>
+          <t>2026-09-03 21:59:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:49</t>
+          <t>2026-09-03 21:59:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:49</t>
+          <t>2026-09-03 21:59:04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:49</t>
+          <t>2026-09-03 21:59:04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:49</t>
+          <t>2026-09-03 21:59:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:49</t>
+          <t>2026-09-03 21:59:04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:49</t>
+          <t>2026-09-03 21:59:04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:51</t>
+          <t>2026-09-03 21:59:05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:51</t>
+          <t>2026-09-03 21:59:05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:51</t>
+          <t>2026-09-03 21:59:05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:51</t>
+          <t>2026-09-03 21:59:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:51</t>
+          <t>2026-09-03 21:59:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:51</t>
+          <t>2026-09-03 21:59:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:51</t>
+          <t>2026-09-03 21:59:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:51</t>
+          <t>2026-09-03 21:59:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:51</t>
+          <t>2026-09-03 21:59:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:51</t>
+          <t>2026-09-03 21:59:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:51</t>
+          <t>2026-09-03 21:59:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:51</t>
+          <t>2026-09-03 21:59:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:51</t>
+          <t>2026-09-03 21:59:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:51</t>
+          <t>2026-09-03 21:59:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:51</t>
+          <t>2026-09-03 21:59:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:52</t>
+          <t>2026-09-03 21:59:07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:52</t>
+          <t>2026-09-03 21:59:07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:52</t>
+          <t>2026-09-03 21:59:07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:52</t>
+          <t>2026-09-03 21:59:07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:52</t>
+          <t>2026-09-03 21:59:07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:52</t>
+          <t>2026-09-03 21:59:07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:52</t>
+          <t>2026-09-03 21:59:07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:52</t>
+          <t>2026-09-03 21:59:07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:52</t>
+          <t>2026-09-03 21:59:07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:52</t>
+          <t>2026-09-03 21:59:07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:52</t>
+          <t>2026-09-03 21:59:07</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:52</t>
+          <t>2026-09-03 21:59:07</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:52</t>
+          <t>2026-09-03 21:59:07</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:52</t>
+          <t>2026-09-03 21:59:07</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:52</t>
+          <t>2026-09-03 21:59:07</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:54</t>
+          <t>2026-09-03 21:59:08</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:54</t>
+          <t>2026-09-03 21:59:08</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:54</t>
+          <t>2026-09-03 21:59:08</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:54</t>
+          <t>2026-09-03 21:59:08</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:54</t>
+          <t>2026-09-03 21:59:08</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:04</t>
+          <t>2026-09-03 22:33:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:04</t>
+          <t>2026-09-03 22:33:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:04</t>
+          <t>2026-09-03 22:33:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:04</t>
+          <t>2026-09-03 22:33:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:04</t>
+          <t>2026-09-03 22:33:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:04</t>
+          <t>2026-09-03 22:33:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:04</t>
+          <t>2026-09-03 22:33:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:04</t>
+          <t>2026-09-03 22:33:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:04</t>
+          <t>2026-09-03 22:33:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:04</t>
+          <t>2026-09-03 22:33:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:04</t>
+          <t>2026-09-03 22:33:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:04</t>
+          <t>2026-09-03 22:33:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:04</t>
+          <t>2026-09-03 22:33:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:04</t>
+          <t>2026-09-03 22:33:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:04</t>
+          <t>2026-09-03 22:33:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:05</t>
+          <t>2026-09-03 22:33:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:05</t>
+          <t>2026-09-03 22:33:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:05</t>
+          <t>2026-09-03 22:33:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:05</t>
+          <t>2026-09-03 22:33:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:05</t>
+          <t>2026-09-03 22:33:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:05</t>
+          <t>2026-09-03 22:33:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:05</t>
+          <t>2026-09-03 22:33:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:05</t>
+          <t>2026-09-03 22:33:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:05</t>
+          <t>2026-09-03 22:33:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:05</t>
+          <t>2026-09-03 22:33:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:05</t>
+          <t>2026-09-03 22:33:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:05</t>
+          <t>2026-09-03 22:33:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:05</t>
+          <t>2026-09-03 22:33:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:05</t>
+          <t>2026-09-03 22:33:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:05</t>
+          <t>2026-09-03 22:33:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:07</t>
+          <t>2026-09-03 22:33:04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:07</t>
+          <t>2026-09-03 22:33:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:07</t>
+          <t>2026-09-03 22:33:04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:07</t>
+          <t>2026-09-03 22:33:04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:07</t>
+          <t>2026-09-03 22:33:04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:07</t>
+          <t>2026-09-03 22:33:04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:07</t>
+          <t>2026-09-03 22:33:04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:07</t>
+          <t>2026-09-03 22:33:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:07</t>
+          <t>2026-09-03 22:33:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:07</t>
+          <t>2026-09-03 22:33:04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:07</t>
+          <t>2026-09-03 22:33:04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:07</t>
+          <t>2026-09-03 22:33:04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:07</t>
+          <t>2026-09-03 22:33:04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:07</t>
+          <t>2026-09-03 22:33:04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:07</t>
+          <t>2026-09-03 22:33:04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:08</t>
+          <t>2026-09-03 22:33:06</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:08</t>
+          <t>2026-09-03 22:33:06</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:08</t>
+          <t>2026-09-03 22:33:06</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:08</t>
+          <t>2026-09-03 22:33:06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:59:08</t>
+          <t>2026-09-03 22:33:06</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:02</t>
+          <t>2026-09-03 22:45:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:02</t>
+          <t>2026-09-03 22:45:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:02</t>
+          <t>2026-09-03 22:45:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:02</t>
+          <t>2026-09-03 22:45:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:02</t>
+          <t>2026-09-03 22:45:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:02</t>
+          <t>2026-09-03 22:45:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:02</t>
+          <t>2026-09-03 22:45:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:02</t>
+          <t>2026-09-03 22:45:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:02</t>
+          <t>2026-09-03 22:45:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:02</t>
+          <t>2026-09-03 22:45:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:02</t>
+          <t>2026-09-03 22:45:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:02</t>
+          <t>2026-09-03 22:45:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:02</t>
+          <t>2026-09-03 22:45:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:02</t>
+          <t>2026-09-03 22:45:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:02</t>
+          <t>2026-09-03 22:45:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:03</t>
+          <t>2026-09-03 22:45:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:03</t>
+          <t>2026-09-03 22:45:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:03</t>
+          <t>2026-09-03 22:45:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:03</t>
+          <t>2026-09-03 22:45:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:03</t>
+          <t>2026-09-03 22:45:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:03</t>
+          <t>2026-09-03 22:45:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:03</t>
+          <t>2026-09-03 22:45:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:03</t>
+          <t>2026-09-03 22:45:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:03</t>
+          <t>2026-09-03 22:45:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:03</t>
+          <t>2026-09-03 22:45:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:03</t>
+          <t>2026-09-03 22:45:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:03</t>
+          <t>2026-09-03 22:45:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:03</t>
+          <t>2026-09-03 22:45:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:03</t>
+          <t>2026-09-03 22:45:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:03</t>
+          <t>2026-09-03 22:45:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:04</t>
+          <t>2026-09-03 22:45:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:04</t>
+          <t>2026-09-03 22:45:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:04</t>
+          <t>2026-09-03 22:45:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:04</t>
+          <t>2026-09-03 22:45:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:04</t>
+          <t>2026-09-03 22:45:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:04</t>
+          <t>2026-09-03 22:45:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:04</t>
+          <t>2026-09-03 22:45:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:04</t>
+          <t>2026-09-03 22:45:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:04</t>
+          <t>2026-09-03 22:45:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:04</t>
+          <t>2026-09-03 22:45:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:04</t>
+          <t>2026-09-03 22:45:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:04</t>
+          <t>2026-09-03 22:45:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:04</t>
+          <t>2026-09-03 22:45:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:04</t>
+          <t>2026-09-03 22:45:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:04</t>
+          <t>2026-09-03 22:45:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:06</t>
+          <t>2026-09-03 22:45:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:06</t>
+          <t>2026-09-03 22:45:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:06</t>
+          <t>2026-09-03 22:45:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:06</t>
+          <t>2026-09-03 22:45:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:33:06</t>
+          <t>2026-09-03 22:45:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:28</t>
+          <t>2026-09-03 23:01:44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:30</t>
+          <t>2026-09-03 23:01:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:31</t>
+          <t>2026-09-03 23:01:47</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:32</t>
+          <t>2026-09-03 23:01:48</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:32</t>
+          <t>2026-09-03 23:01:48</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:32</t>
+          <t>2026-09-03 23:01:48</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:32</t>
+          <t>2026-09-03 23:01:48</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:32</t>
+          <t>2026-09-03 23:01:48</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
